--- a/data-sources/temples.xlsx
+++ b/data-sources/temples.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal Projects\gsb-community\data-sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB0401E-F315-476D-883D-2279ABB90083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BB5B2E-61B5-4CCD-B056-8F227288706F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>temple_id</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Karanakodam Thirumala Devaswom</t>
   </si>
   <si>
-    <t>Central Karanakodam</t>
-  </si>
-  <si>
     <t>Karanakodam Thirumala Devaswom is one of the most revered temples of the GSB community, dedicated to Lord Venkateshwara. The temple is known for its serene spiritual atmosphere, traditional rituals, and grand annual festivals that bring together devotees from across the region.</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>SVB Devi Temple</t>
   </si>
   <si>
-    <t>East Karanakodam</t>
-  </si>
-  <si>
     <t>SVB Devi Temple is a sacred shrine dedicated to Goddess Devi, worshipped as the divine protector of the community. The temple is especially vibrant during Navaratri, featuring cultural programs, special homams, and devotional gatherings that reflect deep spiritual traditions.</t>
   </si>
   <si>
@@ -91,9 +85,6 @@
     <t>shivalayam</t>
   </si>
   <si>
-    <t>West Karanakodam</t>
-  </si>
-  <si>
     <t>Shivalayam is an ancient temple dedicated to Lord Shiva, symbolizing peace, devotion, and inner transformation. Devotees gather here in large numbers during Pradosham and Maha Shivaratri to participate in sacred abhishekams and night-long prayers.</t>
   </si>
   <si>
@@ -112,9 +103,6 @@
     <t>Muthi Bhagavathy Temple</t>
   </si>
   <si>
-    <t>North Karanakodam</t>
-  </si>
-  <si>
     <t>Muthi Bhagavathy Temple is devoted to Goddess Bhagavathy, revered for her divine protection and blessings. The temple holds traditional rituals, community prayers, and vibrant annual celebrations that preserve centuries-old spiritual customs.</t>
   </si>
   <si>
@@ -133,19 +121,28 @@
     <t>Shri Sidhivinayak Mandir</t>
   </si>
   <si>
-    <t>South Karanakodam</t>
-  </si>
-  <si>
     <t>Shri Sidhivinayak Mandir is dedicated to Lord Ganesha, the remover of obstacles and the harbinger of auspicious beginnings. Devotees visit the temple to seek blessings before important life events, examinations, and new ventures.</t>
   </si>
   <si>
-    <t>1) Santhosh Bhat 2) Manoj Bhat</t>
-  </si>
-  <si>
     <t>1) Ganapathi Homam 2) Sankashti Chaturthi Pooja 3) Modaka Offering Seva 4) Vinayaka Chaturthi Mahotsav</t>
   </si>
   <si>
     <t>Shivalayam - Shiva Temple</t>
+  </si>
+  <si>
+    <t>South Janatha Road,  Karanakodam</t>
+  </si>
+  <si>
+    <t>South Janatha Road, Karanakodam</t>
+  </si>
+  <si>
+    <t>Shivalayam Road, Karanakodam</t>
+  </si>
+  <si>
+    <t>TD Sannidhi Road, Karanakodam</t>
+  </si>
+  <si>
+    <t>1) Santhosh Bhat 2) Sreekanth G Bhat</t>
   </si>
 </sst>
 </file>
@@ -178,8 +175,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,6 +519,9 @@
   <cols>
     <col min="2" max="2" width="40.21875" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -531,20 +534,20 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -554,109 +557,109 @@
       <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
+    <row r="4" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
+    <row r="5" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
+    <row r="6" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="G5" t="s">
+      <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="F6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
